--- a/data/trans_orig/P41E_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023</t>
+          <t>Población según si con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023 (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>991</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1679</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3123</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>991</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3466</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3565</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>991</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3527</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -843,97 +843,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1679</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1011</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>1265</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>866</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6921</t>
+          <t>6881</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10009</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24455</t>
+          <t>24639</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15750</t>
+          <t>15489</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27740</t>
+          <t>27222</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28724</t>
+          <t>28100</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47233</t>
+          <t>47560</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>128405</t>
+          <t>128477</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>143059</t>
+          <t>142692</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>121310</t>
+          <t>121117</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>134448</t>
+          <t>134348</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>255033</t>
+          <t>254232</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>274301</t>
+          <t>274613</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,46%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6817</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7250</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7178</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>5277</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>733</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8479</t>
+          <t>8642</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12090</t>
+          <t>12661</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16226</t>
+          <t>16710</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10559</t>
+          <t>10357</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>25166</t>
+          <t>25218</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42987</t>
+          <t>44763</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71115</t>
+          <t>69958</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46432</t>
+          <t>47477</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64950</t>
+          <t>65543</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>96322</t>
+          <t>97946</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130212</t>
+          <t>129389</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>56,67%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38332</t>
+          <t>37941</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>65388</t>
+          <t>65051</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34399</t>
+          <t>33801</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53154</t>
+          <t>51575</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>76996</t>
+          <t>78096</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>109452</t>
+          <t>110197</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,26%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11922</t>
+          <t>12164</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28770</t>
+          <t>29749</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11027</t>
+          <t>11225</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23790</t>
+          <t>23704</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26572</t>
+          <t>25964</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47615</t>
+          <t>46757</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>2437</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10759</t>
+          <t>11451</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>5298</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14441</t>
+          <t>14780</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8873</t>
+          <t>8939</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21594</t>
+          <t>21074</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17323</t>
+          <t>18151</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>36572</t>
+          <t>36956</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29666</t>
+          <t>29301</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>48187</t>
+          <t>47920</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>51726</t>
+          <t>50636</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>78281</t>
+          <t>78574</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25717</t>
+          <t>25881</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45765</t>
+          <t>46144</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30891</t>
+          <t>31473</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50275</t>
+          <t>49976</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>61504</t>
+          <t>62379</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>88811</t>
+          <t>89653</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,69%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>87154</t>
+          <t>87021</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>114495</t>
+          <t>113486</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>77692</t>
+          <t>77829</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>101254</t>
+          <t>100825</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>171951</t>
+          <t>172596</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>208422</t>
+          <t>207515</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>54,83%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>546</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6358</t>
+          <t>6318</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8706</t>
+          <t>8690</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18536</t>
+          <t>18845</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10589</t>
+          <t>10415</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20838</t>
+          <t>21793</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3031</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>3486</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>423</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16847</t>
+          <t>16503</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>33069</t>
+          <t>32548</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19931</t>
+          <t>19959</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34451</t>
+          <t>33753</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>40951</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>62106</t>
+          <t>61082</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21567</t>
+          <t>21007</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43836</t>
+          <t>43135</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21191</t>
+          <t>20619</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35661</t>
+          <t>35839</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>45918</t>
+          <t>45568</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>71874</t>
+          <t>73130</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>97736</t>
+          <t>98106</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>124621</t>
+          <t>124449</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>91612</t>
+          <t>92274</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>112454</t>
+          <t>112387</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>197203</t>
+          <t>195898</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>230713</t>
+          <t>231420</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>68,13%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8328</t>
+          <t>8388</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2831</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>2425</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9738</t>
+          <t>9415</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>486</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>2469</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>683</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>8838</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1816</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6456</t>
+          <t>6408</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>4017</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>12313</t>
+          <t>12722</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>56202</t>
+          <t>56929</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>69033</t>
+          <t>69122</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>66774</t>
+          <t>66456</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>76745</t>
+          <t>76867</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>127228</t>
+          <t>126759</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>143146</t>
+          <t>142928</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,13%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3349</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>12425</t>
+          <t>13053</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>7029</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16070</t>
+          <t>16295</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>12398</t>
+          <t>12323</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>25827</t>
+          <t>25156</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>13709</t>
+          <t>13502</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>28245</t>
+          <t>27765</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>17918</t>
+          <t>17431</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>30234</t>
+          <t>30807</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>33107</t>
+          <t>33198</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>52730</t>
+          <t>52622</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>2425</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>11251</t>
+          <t>10237</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>824</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>6997</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>14126</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>23730</t>
+          <t>22132</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>43689</t>
+          <t>42730</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>18405</t>
+          <t>18496</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>31905</t>
+          <t>32090</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>45561</t>
+          <t>44554</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>69262</t>
+          <t>71163</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>16011</t>
+          <t>16639</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>33267</t>
+          <t>33966</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>10436</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>21605</t>
+          <t>21363</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>30302</t>
+          <t>29983</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>51677</t>
+          <t>50943</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>90937</t>
+          <t>90618</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>115279</t>
+          <t>115922</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>73884</t>
+          <t>73100</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>91019</t>
+          <t>91735</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>170172</t>
+          <t>169340</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>201527</t>
+          <t>201883</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,68%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>939</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>7648</t>
+          <t>7720</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>6552</t>
+          <t>6634</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>11565</t>
+          <t>11179</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>718</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>7543</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>10446</t>
+          <t>9740</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>13289</t>
+          <t>14311</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>7638</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>21068</t>
+          <t>21096</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>30266</t>
+          <t>29524</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>12357</t>
+          <t>11788</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>43787</t>
+          <t>44640</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>99157</t>
+          <t>99125</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>135100</t>
+          <t>135247</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>39714</t>
+          <t>40061</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>211357</t>
+          <t>210240</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>114534</t>
+          <t>108830</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>332434</t>
+          <t>327951</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,29%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>125483</t>
+          <t>125627</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>161370</t>
+          <t>161182</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>250023</t>
+          <t>251415</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>451511</t>
+          <t>450227</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>389896</t>
+          <t>392610</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>642532</t>
+          <t>648370</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>83,62%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>20991</t>
+          <t>19834</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>105522</t>
+          <t>106053</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>53207</t>
+          <t>55362</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>75415</t>
+          <t>78069</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>52220</t>
+          <t>51289</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>174676</t>
+          <t>175977</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>18570</t>
+          <t>16554</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>92845</t>
+          <t>89738</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>34199</t>
+          <t>34973</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>53480</t>
+          <t>53967</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>42337</t>
+          <t>35261</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>134288</t>
+          <t>133360</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>15763</t>
+          <t>16060</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>87550</t>
+          <t>87921</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>36433</t>
+          <t>37120</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>56694</t>
+          <t>55901</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>43837</t>
+          <t>32221</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>135968</t>
+          <t>135063</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,07%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>40931</t>
+          <t>41640</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>219178</t>
+          <t>221052</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>77313</t>
+          <t>75768</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>102372</t>
+          <t>102944</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>93390</t>
+          <t>88857</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>302845</t>
+          <t>301266</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,6%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>103735</t>
+          <t>104880</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>487383</t>
+          <t>495384</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>52007</t>
+          <t>50745</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>78146</t>
+          <t>76351</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>169182</t>
+          <t>168685</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>660434</t>
+          <t>679886</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>75,84%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>64115</t>
+          <t>66021</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>132696</t>
+          <t>134859</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>82298</t>
+          <t>76296</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>146997</t>
+          <t>146786</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>176937</t>
+          <t>172926</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>269334</t>
+          <t>269810</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>39620</t>
+          <t>42588</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>84648</t>
+          <t>84869</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>38092</t>
+          <t>40239</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>76549</t>
+          <t>76625</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>96351</t>
+          <t>93737</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>153837</t>
+          <t>152135</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>93251</t>
+          <t>95933</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>185680</t>
+          <t>189898</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>107609</t>
+          <t>106968</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>199222</t>
+          <t>197019</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>239826</t>
+          <t>236783</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>369225</t>
+          <t>367288</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>291134</t>
+          <t>294676</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>559499</t>
+          <t>559933</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>295654</t>
+          <t>289168</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>510895</t>
+          <t>511166</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>688219</t>
+          <t>678010</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>1042641</t>
+          <t>1041990</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,41%</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>822842</t>
+          <t>817951</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>1261126</t>
+          <t>1251991</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>758941</t>
+          <t>754114</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1136916</t>
+          <t>1165183</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1612295</t>
+          <t>1606545</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>2225227</t>
+          <t>2231183</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>65,13%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P41E_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023-Provincia-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>984</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>3138</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>984</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>766</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>5030</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3493</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1446</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>6734</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16219</t>
+          <t>21750</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>13926</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24639</t>
+          <t>29907</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20919</t>
+          <t>26811</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15489</t>
+          <t>20237</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27222</t>
+          <t>34852</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>37138</t>
+          <t>48561</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28100</t>
+          <t>38617</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47560</t>
+          <t>59032</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>136777</t>
+          <t>134493</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>128477</t>
+          <t>126064</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>142692</t>
+          <t>142251</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>128394</t>
+          <t>133178</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>121117</t>
+          <t>124892</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>134348</t>
+          <t>140018</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>265171</t>
+          <t>267671</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>254232</t>
+          <t>256879</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>274613</t>
+          <t>277890</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>86,45%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>153164</t>
+          <t>157008</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>153164</t>
+          <t>157008</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>153164</t>
+          <t>157008</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>153797</t>
+          <t>164449</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>153797</t>
+          <t>164449</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>153797</t>
+          <t>164449</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>306961</t>
+          <t>321457</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>306961</t>
+          <t>321457</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>306961</t>
+          <t>321457</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7072</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>596</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1467,42 +1467,42 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1862</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>6903</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>2,88%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1856</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>7781</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>7593</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>4802</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>705</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8642</t>
+          <t>7916</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12661</t>
+          <t>17871</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10781</t>
+          <t>11146</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>6181</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16710</t>
+          <t>16811</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>16138</t>
+          <t>19364</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10357</t>
+          <t>12379</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>25218</t>
+          <t>28658</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>57768</t>
+          <t>60677</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44763</t>
+          <t>46817</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69958</t>
+          <t>74932</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>55956</t>
+          <t>59442</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47477</t>
+          <t>49099</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65543</t>
+          <t>68209</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>113724</t>
+          <t>120118</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97946</t>
+          <t>104608</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>129389</t>
+          <t>137212</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>57,29%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>50677</t>
+          <t>50382</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37941</t>
+          <t>35822</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>65051</t>
+          <t>64265</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>43122</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33801</t>
+          <t>36649</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51575</t>
+          <t>54022</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>93799</t>
+          <t>95364</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>78096</t>
+          <t>78693</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>110197</t>
+          <t>111522</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>46,56%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>116409</t>
+          <t>121875</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>116409</t>
+          <t>121875</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>116409</t>
+          <t>121875</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>111925</t>
+          <t>117642</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>111925</t>
+          <t>117642</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>111925</t>
+          <t>117642</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>228334</t>
+          <t>239516</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>228334</t>
+          <t>239516</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>228334</t>
+          <t>239516</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>19125</t>
+          <t>17917</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12164</t>
+          <t>11316</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29749</t>
+          <t>27122</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16702</t>
+          <t>16648</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11225</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23704</t>
+          <t>24619</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>35828</t>
+          <t>34565</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25964</t>
+          <t>24708</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46757</t>
+          <t>45145</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5525</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2437</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11451</t>
+          <t>10532</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>8712</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5298</t>
+          <t>4912</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14780</t>
+          <t>13223</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>14198</t>
+          <t>14024</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8939</t>
+          <t>8963</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21074</t>
+          <t>21147</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>26429</t>
+          <t>28682</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18151</t>
+          <t>19750</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>36956</t>
+          <t>39965</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>37518</t>
+          <t>37699</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29301</t>
+          <t>29088</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>47920</t>
+          <t>46975</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>63947</t>
+          <t>66381</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>50636</t>
+          <t>54092</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>78574</t>
+          <t>81078</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>34884</t>
+          <t>34765</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25881</t>
+          <t>25795</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46144</t>
+          <t>45710</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>39749</t>
+          <t>41069</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31473</t>
+          <t>32014</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49976</t>
+          <t>50417</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>74633</t>
+          <t>75834</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>62379</t>
+          <t>62329</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>89653</t>
+          <t>90081</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>100096</t>
+          <t>102154</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>87021</t>
+          <t>88494</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>113486</t>
+          <t>116724</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>89768</t>
+          <t>93129</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>77829</t>
+          <t>81117</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>100825</t>
+          <t>104879</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>189864</t>
+          <t>195283</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>172596</t>
+          <t>177930</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>207515</t>
+          <t>213145</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>55,21%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>186059</t>
+          <t>188829</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>186059</t>
+          <t>188829</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>186059</t>
+          <t>188829</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>192411</t>
+          <t>197257</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>192411</t>
+          <t>197257</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>192411</t>
+          <t>197257</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>378470</t>
+          <t>386087</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>378470</t>
+          <t>386087</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>378470</t>
+          <t>386087</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>589</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6318</t>
+          <t>6289</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>12904</t>
+          <t>14047</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8690</t>
+          <t>9755</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18845</t>
+          <t>20677</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>15060</t>
+          <t>16176</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10415</t>
+          <t>11260</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21793</t>
+          <t>23475</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3031</t>
+          <t>4846</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2929,12 +2929,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>3828</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>595</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4687</t>
+          <t>6082</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>23683</t>
+          <t>23804</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16503</t>
+          <t>16861</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32548</t>
+          <t>32472</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>26472</t>
+          <t>28973</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19959</t>
+          <t>22087</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33753</t>
+          <t>37727</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>50155</t>
+          <t>52777</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>43238</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>61082</t>
+          <t>64322</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>30882</t>
+          <t>34013</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21007</t>
+          <t>23955</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43135</t>
+          <t>47607</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>27664</t>
+          <t>31545</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20619</t>
+          <t>23511</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35839</t>
+          <t>39943</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>58546</t>
+          <t>65558</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>45568</t>
+          <t>52132</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>73130</t>
+          <t>81311</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>111827</t>
+          <t>134241</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>98106</t>
+          <t>119520</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>124449</t>
+          <t>147225</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>102340</t>
+          <t>113227</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>92274</t>
+          <t>101558</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>112387</t>
+          <t>124470</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>214167</t>
+          <t>247467</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>195898</t>
+          <t>229781</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>231420</t>
+          <t>265527</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>69,1%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>169279</t>
+          <t>195358</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>169279</t>
+          <t>195358</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>169279</t>
+          <t>195358</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>170396</t>
+          <t>188906</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>170396</t>
+          <t>188906</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>170396</t>
+          <t>188906</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>339675</t>
+          <t>384264</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>339675</t>
+          <t>384264</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>339675</t>
+          <t>384264</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>4132</t>
+          <t>4565</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8388</t>
+          <t>9487</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>5071</t>
+          <t>5609</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2425</t>
+          <t>2768</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9415</t>
+          <t>10347</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>509</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>6124</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>405</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2469</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>709</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6103</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8838</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3590</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1683</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6408</t>
+          <t>6675</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7114</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>12722</t>
+          <t>12736</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>63395</t>
+          <t>70056</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>56929</t>
+          <t>62413</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>69122</t>
+          <t>75530</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>72138</t>
+          <t>78960</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>66456</t>
+          <t>71779</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>76867</t>
+          <t>84103</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>135533</t>
+          <t>149016</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>126759</t>
+          <t>139751</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>142928</t>
+          <t>156957</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,26%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>6993</t>
+          <t>7554</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>13053</t>
+          <t>13554</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>10937</t>
+          <t>12075</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16295</t>
+          <t>18346</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>17930</t>
+          <t>19629</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>12323</t>
+          <t>13440</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>25156</t>
+          <t>28154</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,29%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>79898</t>
+          <t>87857</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>79898</t>
+          <t>87857</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>79898</t>
+          <t>87857</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>87992</t>
+          <t>96234</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>87992</t>
+          <t>96234</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>87992</t>
+          <t>96234</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>167890</t>
+          <t>184091</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>167890</t>
+          <t>184091</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>167890</t>
+          <t>184091</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>19483</t>
+          <t>20245</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>13502</t>
+          <t>14110</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>27765</t>
+          <t>28869</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>23012</t>
+          <t>23343</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>17431</t>
+          <t>17062</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>30807</t>
+          <t>30864</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>42496</t>
+          <t>43588</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>33198</t>
+          <t>34981</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>52622</t>
+          <t>53145</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2425</t>
+          <t>2266</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>10237</t>
+          <t>9803</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>587</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6997</t>
+          <t>6519</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>8062</t>
+          <t>7812</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>14126</t>
+          <t>13469</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>31862</t>
+          <t>30676</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>22132</t>
+          <t>21763</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>42730</t>
+          <t>41609</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>24605</t>
+          <t>25345</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>18496</t>
+          <t>18921</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>32090</t>
+          <t>33178</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>56467</t>
+          <t>56022</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>44554</t>
+          <t>45498</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>71163</t>
+          <t>69838</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>20,72%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>23859</t>
+          <t>23535</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>16639</t>
+          <t>15008</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>33966</t>
+          <t>32459</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>15333</t>
+          <t>16398</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>10244</t>
+          <t>11167</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>21363</t>
+          <t>22238</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>39192</t>
+          <t>39933</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>29983</t>
+          <t>30849</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>50943</t>
+          <t>51773</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>103857</t>
+          <t>106225</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>90618</t>
+          <t>93586</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>115922</t>
+          <t>117392</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>82652</t>
+          <t>83554</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>73100</t>
+          <t>74231</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>91735</t>
+          <t>93401</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>186509</t>
+          <t>189780</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>169340</t>
+          <t>173074</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>201883</t>
+          <t>203792</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,45%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>184589</t>
+          <t>186011</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>184589</t>
+          <t>186011</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>184589</t>
+          <t>186011</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>148137</t>
+          <t>151123</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>148137</t>
+          <t>151123</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>148137</t>
+          <t>151123</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>332725</t>
+          <t>337134</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>332725</t>
+          <t>337134</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>332725</t>
+          <t>337134</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,102 +4817,102 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>2911</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>931</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>7720</t>
+          <t>8577</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>2713</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>6874</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>5554</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>2324</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>10638</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>2531</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>6634</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>5442</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>1589</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>11179</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -4930,67 +4930,67 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>2447</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>823</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>3074</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>9545</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
           <t>0,88%</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>2959</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>9740</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>14311</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>13352</t>
+          <t>18696</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>7459</t>
+          <t>10938</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>21096</t>
+          <t>31038</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>15277</t>
+          <t>16742</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>10596</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>29524</t>
+          <t>25148</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>28629</t>
+          <t>35439</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>11788</t>
+          <t>25307</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>44640</t>
+          <t>48194</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>116782</t>
+          <t>133575</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>99125</t>
+          <t>114041</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>135247</t>
+          <t>154165</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>118900</t>
+          <t>143146</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>40061</t>
+          <t>125631</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>210240</t>
+          <t>159795</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>235682</t>
+          <t>276721</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>108830</t>
+          <t>250450</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>327951</t>
+          <t>302865</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>44,88%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>143545</t>
+          <t>167899</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>125627</t>
+          <t>148007</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>161182</t>
+          <t>189241</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>356714</t>
+          <t>183550</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>251415</t>
+          <t>166267</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>450227</t>
+          <t>202112</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>500259</t>
+          <t>351448</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>392610</t>
+          <t>325764</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>648370</t>
+          <t>377208</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>55,89%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>279037</t>
+          <t>325660</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>279037</t>
+          <t>325660</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>279037</t>
+          <t>325660</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>496380</t>
+          <t>349225</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>496380</t>
+          <t>349225</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>496380</t>
+          <t>349225</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>775417</t>
+          <t>674885</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>775417</t>
+          <t>674885</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>775417</t>
+          <t>674885</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,32 +5499,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>58236</t>
+          <t>65123</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>19834</t>
+          <t>51944</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>106053</t>
+          <t>77945</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5534,32 +5534,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>65043</t>
+          <t>74521</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>55362</t>
+          <t>62140</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>78069</t>
+          <t>87452</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>123279</t>
+          <t>139644</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>51289</t>
+          <t>122509</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>175977</t>
+          <t>158062</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>49635</t>
+          <t>54522</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>16554</t>
+          <t>43650</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>89738</t>
+          <t>68606</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>43349</t>
+          <t>49479</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>34973</t>
+          <t>38594</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>53967</t>
+          <t>60790</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>92984</t>
+          <t>104002</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>35261</t>
+          <t>88709</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>133360</t>
+          <t>122569</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>48055</t>
+          <t>53771</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>16060</t>
+          <t>42785</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>87921</t>
+          <t>67943</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>45767</t>
+          <t>53786</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>37120</t>
+          <t>43073</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>67534</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>93822</t>
+          <t>107557</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>32221</t>
+          <t>91160</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>135063</t>
+          <t>125433</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>123546</t>
+          <t>145657</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>41640</t>
+          <t>125027</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>221052</t>
+          <t>164918</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>89286</t>
+          <t>105409</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>75768</t>
+          <t>92103</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>102944</t>
+          <t>123090</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>212831</t>
+          <t>251066</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>88857</t>
+          <t>229622</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>301266</t>
+          <t>278475</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>37,16%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>310755</t>
+          <t>77267</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>104880</t>
+          <t>60675</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>495384</t>
+          <t>96764</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>62824</t>
+          <t>69947</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>50745</t>
+          <t>56731</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>76351</t>
+          <t>85214</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>373579</t>
+          <t>147214</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>168685</t>
+          <t>124935</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>679886</t>
+          <t>169235</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>590227</t>
+          <t>396341</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>590227</t>
+          <t>396341</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>590227</t>
+          <t>396341</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>306269</t>
+          <t>353142</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>306269</t>
+          <t>353142</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>306269</t>
+          <t>353142</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>896495</t>
+          <t>749483</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>896495</t>
+          <t>749483</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>896495</t>
+          <t>749483</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6181,32 +6181,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>107335</t>
+          <t>114086</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>66021</t>
+          <t>96482</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>134859</t>
+          <t>133023</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6216,32 +6216,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>122688</t>
+          <t>133895</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>76296</t>
+          <t>117722</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>146786</t>
+          <t>152309</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>230023</t>
+          <t>247981</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>172926</t>
+          <t>223971</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>269810</t>
+          <t>275122</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -6294,32 +6294,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>67036</t>
+          <t>72339</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>42588</t>
+          <t>58025</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>84869</t>
+          <t>86950</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>60419</t>
+          <t>66744</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>40239</t>
+          <t>53818</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>76625</t>
+          <t>79844</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>127455</t>
+          <t>139083</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>93737</t>
+          <t>121019</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>152135</t>
+          <t>161332</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -6407,32 +6407,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>152429</t>
+          <t>168271</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>95933</t>
+          <t>143513</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>189898</t>
+          <t>189431</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6442,32 +6442,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>167503</t>
+          <t>180917</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>106968</t>
+          <t>159847</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>197019</t>
+          <t>201626</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>319932</t>
+          <t>349189</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>236783</t>
+          <t>317876</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>367288</t>
+          <t>381411</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -6520,32 +6520,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>467334</t>
+          <t>524027</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>294676</t>
+          <t>485206</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>559933</t>
+          <t>563621</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6555,32 +6555,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>439945</t>
+          <t>502780</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>289168</t>
+          <t>471577</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>511166</t>
+          <t>532257</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>907279</t>
+          <t>1026807</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>678010</t>
+          <t>977498</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>1041990</t>
+          <t>1079154</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>32,93%</t>
         </is>
       </c>
     </row>
@@ -6633,32 +6633,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>964527</t>
+          <t>780215</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>817951</t>
+          <t>737074</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>1251991</t>
+          <t>821380</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6668,32 +6668,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>876751</t>
+          <t>733642</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>754114</t>
+          <t>697805</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1165183</t>
+          <t>767634</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,32 +6703,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>1841278</t>
+          <t>1513856</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1606545</t>
+          <t>1460505</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>2231183</t>
+          <t>1567867</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>47,85%</t>
         </is>
       </c>
     </row>
@@ -6746,17 +6746,17 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>1758661</t>
+          <t>1658938</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>1758661</t>
+          <t>1658938</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>1758661</t>
+          <t>1658938</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6781,17 +6781,17 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>1667306</t>
+          <t>1617978</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>1667306</t>
+          <t>1617978</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>1667306</t>
+          <t>1617978</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>3425967</t>
+          <t>3276916</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>3425967</t>
+          <t>3276916</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>3425967</t>
+          <t>3276916</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">

--- a/data/trans_orig/P41E_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023 (tasa de respuesta: 69,32%)</t>
+          <t>Población según su nivel de acuerdo sobre la satisfacción de sus relaciones sexuales por ambas partes en el último mes en 2023 (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
